--- a/src/test/resources/data/registerData/registerData.xlsx
+++ b/src/test/resources/data/registerData/registerData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Documents\Automation\ParaBank\src\test\resources\data\registerData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B7A938-1027-4A1E-8FD6-4A252D512CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB7C310-2A7B-43AE-A822-BC3713AE55FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1455" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>FIRSTNAME</t>
-  </si>
-  <si>
-    <t>LASTNAME</t>
-  </si>
-  <si>
     <t>ADDRESS</t>
   </si>
   <si>
@@ -45,9 +39,6 @@
     <t>STATE</t>
   </si>
   <si>
-    <t>ZIPCODE</t>
-  </si>
-  <si>
     <t>SSN</t>
   </si>
   <si>
@@ -57,12 +48,6 @@
     <t>PASSWORD</t>
   </si>
   <si>
-    <t>PASSWORDCONFIRM</t>
-  </si>
-  <si>
-    <t>PHONENUMBER</t>
-  </si>
-  <si>
     <t>CP01</t>
   </si>
   <si>
@@ -88,14 +73,286 @@
   </si>
   <si>
     <t>AUTO</t>
+  </si>
+  <si>
+    <t>CP02</t>
+  </si>
+  <si>
+    <t>CP03</t>
+  </si>
+  <si>
+    <t>CP04</t>
+  </si>
+  <si>
+    <t>Hector</t>
+  </si>
+  <si>
+    <t>Larrazabal</t>
+  </si>
+  <si>
+    <t>5449 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11234567891</t>
+  </si>
+  <si>
+    <t>078-05-1121</t>
+  </si>
+  <si>
+    <t>Tomas</t>
+  </si>
+  <si>
+    <t>Insaurralde</t>
+  </si>
+  <si>
+    <t>5359 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11234567892</t>
+  </si>
+  <si>
+    <t>078-05-1125</t>
+  </si>
+  <si>
+    <t>CP05</t>
+  </si>
+  <si>
+    <t>CP06</t>
+  </si>
+  <si>
+    <t>CP07</t>
+  </si>
+  <si>
+    <t>CP08</t>
+  </si>
+  <si>
+    <t>CP09</t>
+  </si>
+  <si>
+    <t>CP10</t>
+  </si>
+  <si>
+    <t>CP11</t>
+  </si>
+  <si>
+    <t>CP12</t>
+  </si>
+  <si>
+    <t>CP13</t>
+  </si>
+  <si>
+    <t>CP14</t>
+  </si>
+  <si>
+    <t>CP15</t>
+  </si>
+  <si>
+    <t>+11234567893</t>
+  </si>
+  <si>
+    <t>091-05-1120</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>023-30-1122</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t>Hernandez</t>
+  </si>
+  <si>
+    <t>5669 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11334567393</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>Mambeira</t>
+  </si>
+  <si>
+    <t>+11234777892</t>
+  </si>
+  <si>
+    <t>998-05-1120</t>
+  </si>
+  <si>
+    <t>Balanta</t>
+  </si>
+  <si>
+    <t>Sabeiro</t>
+  </si>
+  <si>
+    <t>5222 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11233367892</t>
+  </si>
+  <si>
+    <t>078-05-9999</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>Fernandez</t>
+  </si>
+  <si>
+    <t>5553 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>078-05-2222</t>
+  </si>
+  <si>
+    <t>Agustina</t>
+  </si>
+  <si>
+    <t>Kinoto</t>
+  </si>
+  <si>
+    <t>1349 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11234507893</t>
+  </si>
+  <si>
+    <t>Lisandro</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>4359 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11111567892</t>
+  </si>
+  <si>
+    <t>078-05-2121</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Gibraltar</t>
+  </si>
+  <si>
+    <t>5450 NW 72nd Ave</t>
+  </si>
+  <si>
+    <t>+11235677892</t>
+  </si>
+  <si>
+    <t>099-99-1120</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>Garibaldi</t>
+  </si>
+  <si>
+    <t>078-05-1024</t>
+  </si>
+  <si>
+    <t>Masuyama</t>
+  </si>
+  <si>
+    <t>Canteira</t>
+  </si>
+  <si>
+    <t>+11994567892</t>
+  </si>
+  <si>
+    <t>078-05-3251</t>
+  </si>
+  <si>
+    <t>hugocanteira</t>
+  </si>
+  <si>
+    <t>PASSWORD_CONFIRM</t>
+  </si>
+  <si>
+    <t>PHONE_NUMBER</t>
+  </si>
+  <si>
+    <t>ZIP_CODE</t>
+  </si>
+  <si>
+    <t>FIRST_NAME</t>
+  </si>
+  <si>
+    <t>LAST_NAME</t>
+  </si>
+  <si>
+    <t>FIRST_NAME_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>LAST_NAME_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>ADDRESS_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>CITY_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>STATE_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>ZIP_CODE_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>SSN_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>USERNAME_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>PASSWORD_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>PASSWORD_CONFIRM_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>EXPECTED_MESSAGE</t>
+  </si>
+  <si>
+    <t>REGISTRATION_SUCCESS</t>
+  </si>
+  <si>
+    <t>EXISTING_USER_ERROR</t>
+  </si>
+  <si>
+    <t>FIRST_NAME_REQUIRED_ERROR;LAST_NAME_REQUIRED_ERROR;ADDRESS_REQUIRED_ERROR;CITY_REQUIRED_ERROR;STATE_REQUIRED_ERROR;ZIP_CODE_REQUIRED_ERROR;SSN_REQUIRED_ERROR;USERNAME_REQUIRED_ERROR;PASSWORD_REQUIRED_ERROR;PASSWORD_CONFIRM_REQUIRED_ERROR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -123,9 +380,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,100 +664,619 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
       </c>
       <c r="G2">
         <v>33166</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>12345</v>
+      </c>
+      <c r="L2">
+        <v>12345</v>
+      </c>
+      <c r="M2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>33163</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3">
+        <v>12345</v>
+      </c>
+      <c r="L3">
+        <v>12345</v>
+      </c>
+      <c r="M3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="J4" s="2"/>
+      <c r="M4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2">
-        <v>12345</v>
-      </c>
-      <c r="L2">
-        <v>12345</v>
-      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>33165</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>12345</v>
+      </c>
+      <c r="L5">
+        <v>12345</v>
+      </c>
+      <c r="M5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>33160</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>12345</v>
+      </c>
+      <c r="L6">
+        <v>12345</v>
+      </c>
+      <c r="M6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>20000</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>12345</v>
+      </c>
+      <c r="L7">
+        <v>12345</v>
+      </c>
+      <c r="M7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>33163</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>12345</v>
+      </c>
+      <c r="L8">
+        <v>12345</v>
+      </c>
+      <c r="M8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>33773</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>12345</v>
+      </c>
+      <c r="L9">
+        <v>12345</v>
+      </c>
+      <c r="M9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>12345</v>
+      </c>
+      <c r="L10">
+        <v>12345</v>
+      </c>
+      <c r="M10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>14163</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11">
+        <v>12345</v>
+      </c>
+      <c r="L11">
+        <v>12345</v>
+      </c>
+      <c r="M11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>35164</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12">
+        <v>12345</v>
+      </c>
+      <c r="L12">
+        <v>12345</v>
+      </c>
+      <c r="M12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>32263</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13">
+        <v>12345</v>
+      </c>
+      <c r="L13">
+        <v>12345</v>
+      </c>
+      <c r="M13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>22163</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14">
+        <v>12345</v>
+      </c>
+      <c r="M14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>10163</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>12345</v>
+      </c>
+      <c r="M15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>33163</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16">
+        <v>12345</v>
+      </c>
+      <c r="L16">
+        <v>12346</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/test/resources/data/registerData/registerData.xlsx
+++ b/src/test/resources/data/registerData/registerData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Documents\Automation\ParaBank\src\test\resources\data\registerData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB7C310-2A7B-43AE-A822-BC3713AE55FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C008CD99-B117-4F9B-A376-9B20E5AD4C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3570" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>FIRST_NAME_REQUIRED_ERROR;LAST_NAME_REQUIRED_ERROR;ADDRESS_REQUIRED_ERROR;CITY_REQUIRED_ERROR;STATE_REQUIRED_ERROR;ZIP_CODE_REQUIRED_ERROR;SSN_REQUIRED_ERROR;USERNAME_REQUIRED_ERROR;PASSWORD_REQUIRED_ERROR;PASSWORD_CONFIRM_REQUIRED_ERROR</t>
+  </si>
+  <si>
+    <t>PASSWORDS_MISMATCH_ERROR</t>
   </si>
 </sst>
 </file>
@@ -1271,6 +1274,9 @@
       <c r="L16">
         <v>12346</v>
       </c>
+      <c r="M16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>

--- a/src/test/resources/data/registerData/registerData.xlsx
+++ b/src/test/resources/data/registerData/registerData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\Desktop\Documents\Automation\ParaBank\src\test\resources\data\registerData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C008CD99-B117-4F9B-A376-9B20E5AD4C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F6BCA5-BF3B-44B5-9B10-E3F30DC552A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="147">
   <si>
     <t>ID</t>
   </si>
@@ -51,9 +51,6 @@
     <t>CP01</t>
   </si>
   <si>
-    <t>Rodrigo</t>
-  </si>
-  <si>
     <t>Zabaleta</t>
   </si>
   <si>
@@ -84,36 +81,12 @@
     <t>CP04</t>
   </si>
   <si>
-    <t>Hector</t>
-  </si>
-  <si>
-    <t>Larrazabal</t>
-  </si>
-  <si>
-    <t>5449 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>+11234567891</t>
-  </si>
-  <si>
-    <t>078-05-1121</t>
-  </si>
-  <si>
     <t>Tomas</t>
   </si>
   <si>
     <t>Insaurralde</t>
   </si>
   <si>
-    <t>5359 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>+11234567892</t>
-  </si>
-  <si>
-    <t>078-05-1125</t>
-  </si>
-  <si>
     <t>CP05</t>
   </si>
   <si>
@@ -147,135 +120,36 @@
     <t>CP15</t>
   </si>
   <si>
-    <t>+11234567893</t>
-  </si>
-  <si>
-    <t>091-05-1120</t>
-  </si>
-  <si>
-    <t>Marcos</t>
-  </si>
-  <si>
-    <t>023-30-1122</t>
-  </si>
-  <si>
-    <t>Mauricio</t>
-  </si>
-  <si>
     <t>Hernandez</t>
   </si>
   <si>
-    <t>5669 NW 72nd Ave</t>
-  </si>
-  <si>
     <t>+11334567393</t>
   </si>
   <si>
-    <t>Cristian</t>
-  </si>
-  <si>
     <t>Mambeira</t>
   </si>
   <si>
-    <t>+11234777892</t>
-  </si>
-  <si>
-    <t>998-05-1120</t>
-  </si>
-  <si>
-    <t>Balanta</t>
-  </si>
-  <si>
     <t>Sabeiro</t>
   </si>
   <si>
-    <t>5222 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>+11233367892</t>
-  </si>
-  <si>
-    <t>078-05-9999</t>
-  </si>
-  <si>
     <t>Gabriela</t>
   </si>
   <si>
     <t>Fernandez</t>
   </si>
   <si>
-    <t>5553 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>078-05-2222</t>
-  </si>
-  <si>
-    <t>Agustina</t>
-  </si>
-  <si>
     <t>Kinoto</t>
   </si>
   <si>
-    <t>1349 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>+11234507893</t>
-  </si>
-  <si>
-    <t>Lisandro</t>
-  </si>
-  <si>
-    <t>Martinez</t>
-  </si>
-  <si>
-    <t>4359 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>+11111567892</t>
-  </si>
-  <si>
-    <t>078-05-2121</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
     <t>Gibraltar</t>
   </si>
   <si>
-    <t>5450 NW 72nd Ave</t>
-  </si>
-  <si>
-    <t>+11235677892</t>
-  </si>
-  <si>
-    <t>099-99-1120</t>
-  </si>
-  <si>
     <t>Fernando</t>
   </si>
   <si>
     <t>Garibaldi</t>
   </si>
   <si>
-    <t>078-05-1024</t>
-  </si>
-  <si>
-    <t>Masuyama</t>
-  </si>
-  <si>
-    <t>Canteira</t>
-  </si>
-  <si>
-    <t>+11994567892</t>
-  </si>
-  <si>
-    <t>078-05-3251</t>
-  </si>
-  <si>
-    <t>hugocanteira</t>
-  </si>
-  <si>
     <t>PASSWORD_CONFIRM</t>
   </si>
   <si>
@@ -334,6 +208,264 @@
   </si>
   <si>
     <t>PASSWORDS_MISMATCH_ERROR</t>
+  </si>
+  <si>
+    <t>Rodrigo Basanta</t>
+  </si>
+  <si>
+    <t>1134 Greenwood St</t>
+  </si>
+  <si>
+    <t>Old City</t>
+  </si>
+  <si>
+    <t>Veen</t>
+  </si>
+  <si>
+    <t>+12424332522</t>
+  </si>
+  <si>
+    <t>021-49-2043</t>
+  </si>
+  <si>
+    <t>mgoncalves</t>
+  </si>
+  <si>
+    <t>Martin Hector</t>
+  </si>
+  <si>
+    <t>Goncalves</t>
+  </si>
+  <si>
+    <t>secretPassword</t>
+  </si>
+  <si>
+    <t>asdK300</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>3493 Sale Street 32</t>
+  </si>
+  <si>
+    <t>+13441125346</t>
+  </si>
+  <si>
+    <t>233-12-3545</t>
+  </si>
+  <si>
+    <t>2026pskey</t>
+  </si>
+  <si>
+    <t>900 Street</t>
+  </si>
+  <si>
+    <t>Lockdown</t>
+  </si>
+  <si>
+    <t>Modern City</t>
+  </si>
+  <si>
+    <t>+11410556923</t>
+  </si>
+  <si>
+    <t>091-01-0009</t>
+  </si>
+  <si>
+    <t>passwordRepeat</t>
+  </si>
+  <si>
+    <t>Marcos Abelairas</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Cabe</t>
+  </si>
+  <si>
+    <t>003-22-0192</t>
+  </si>
+  <si>
+    <t>noStreetPassword</t>
+  </si>
+  <si>
+    <t>Mauricio Balanta</t>
+  </si>
+  <si>
+    <t>5669 NW 33nd Ave</t>
+  </si>
+  <si>
+    <t>023-30-1922</t>
+  </si>
+  <si>
+    <t>automationPassword</t>
+  </si>
+  <si>
+    <t>Cristian Segovia</t>
+  </si>
+  <si>
+    <t>Preston Street 5050</t>
+  </si>
+  <si>
+    <t>Preston City</t>
+  </si>
+  <si>
+    <t>North Bell</t>
+  </si>
+  <si>
+    <t>+11934717890</t>
+  </si>
+  <si>
+    <t>998-05-6407</t>
+  </si>
+  <si>
+    <t>StrongPassword</t>
+  </si>
+  <si>
+    <t>Gregorio Rivadavia</t>
+  </si>
+  <si>
+    <t>Alabama Street 99</t>
+  </si>
+  <si>
+    <t>New Tax</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>+19233117822</t>
+  </si>
+  <si>
+    <t>153-74-2222</t>
+  </si>
+  <si>
+    <t>bearPassword</t>
+  </si>
+  <si>
+    <t>secretFile</t>
+  </si>
+  <si>
+    <t>Big</t>
+  </si>
+  <si>
+    <t>Big City</t>
+  </si>
+  <si>
+    <t>Sendero 33</t>
+  </si>
+  <si>
+    <t>Sendero</t>
+  </si>
+  <si>
+    <t>021-05-9999</t>
+  </si>
+  <si>
+    <t>nextPassword</t>
+  </si>
+  <si>
+    <t>Agustina Lara</t>
+  </si>
+  <si>
+    <t>1349 NW 44nd Ave</t>
+  </si>
+  <si>
+    <t>+11235507893</t>
+  </si>
+  <si>
+    <t>lockedUser</t>
+  </si>
+  <si>
+    <t>Lisandro Pereira</t>
+  </si>
+  <si>
+    <t>Belaustegui</t>
+  </si>
+  <si>
+    <t>Arnold B 25</t>
+  </si>
+  <si>
+    <t>South Door</t>
+  </si>
+  <si>
+    <t>Door</t>
+  </si>
+  <si>
+    <t>+11111561892</t>
+  </si>
+  <si>
+    <t>099-25-2121</t>
+  </si>
+  <si>
+    <t>longPassword99</t>
+  </si>
+  <si>
+    <t>Martin Ismael</t>
+  </si>
+  <si>
+    <t>Street 40 GB</t>
+  </si>
+  <si>
+    <t>GB City</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>122-29-4420</t>
+  </si>
+  <si>
+    <t>noPassword</t>
+  </si>
+  <si>
+    <t>422 St New Born 40</t>
+  </si>
+  <si>
+    <t>Born City</t>
+  </si>
+  <si>
+    <t>Legion</t>
+  </si>
+  <si>
+    <t>+11734567322</t>
+  </si>
+  <si>
+    <t>001-01-1024</t>
+  </si>
+  <si>
+    <t>noConfirmPassword</t>
+  </si>
+  <si>
+    <t>Sergei</t>
+  </si>
+  <si>
+    <t>Primorsky</t>
+  </si>
+  <si>
+    <t>Chekannaya 4003</t>
+  </si>
+  <si>
+    <t>Tarkov</t>
+  </si>
+  <si>
+    <t>Norvinsk Special Economic Zone</t>
+  </si>
+  <si>
+    <t>+11895660892</t>
+  </si>
+  <si>
+    <t>+10225137292</t>
+  </si>
+  <si>
+    <t>+10330527992</t>
+  </si>
+  <si>
+    <t>846-31-3251</t>
+  </si>
+  <si>
+    <t>usecPassword</t>
   </si>
 </sst>
 </file>
@@ -671,16 +803,16 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -690,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -705,10 +837,10 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
@@ -720,10 +852,10 @@
         <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="M1" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -731,551 +863,557 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2">
         <v>33166</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2">
-        <v>12345</v>
-      </c>
-      <c r="L2">
-        <v>12345</v>
+      <c r="K2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
       </c>
       <c r="M2" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>33163</v>
+        <v>14554</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="J3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K3">
-        <v>12345</v>
-      </c>
-      <c r="L3">
-        <v>12345</v>
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" t="s">
+        <v>71</v>
       </c>
       <c r="M3" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1"/>
       <c r="J4" s="2"/>
       <c r="M4" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="G5">
-        <v>33165</v>
+        <v>13521</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>12345</v>
-      </c>
-      <c r="L5">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
       </c>
       <c r="M5" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="G6">
-        <v>33160</v>
+        <v>23169</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>12345</v>
-      </c>
-      <c r="L6">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="G7">
         <v>20000</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="I7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" t="s">
         <v>14</v>
       </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7">
-        <v>12345</v>
-      </c>
-      <c r="L7">
-        <v>12345</v>
+      <c r="K7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" t="s">
+        <v>87</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>33163</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8">
-        <v>12345</v>
-      </c>
-      <c r="L8">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" t="s">
+        <v>91</v>
       </c>
       <c r="M8" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>94</v>
+      </c>
+      <c r="F9" t="s">
+        <v>95</v>
       </c>
       <c r="G9">
-        <v>33773</v>
+        <v>99773</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" t="s">
+        <v>98</v>
+      </c>
+      <c r="M9" t="s">
         <v>50</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9">
-        <v>12345</v>
-      </c>
-      <c r="L9">
-        <v>12345</v>
-      </c>
-      <c r="M9" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>107</v>
+      </c>
+      <c r="G10">
+        <v>22325</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="I10" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10">
-        <v>12345</v>
-      </c>
-      <c r="L10">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" t="s">
+        <v>106</v>
       </c>
       <c r="M10" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="G11">
         <v>14163</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11">
-        <v>12345</v>
-      </c>
-      <c r="L11">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K11" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" t="s">
+        <v>112</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12">
         <v>35164</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12">
-        <v>12345</v>
-      </c>
-      <c r="L12">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K12" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" t="s">
+        <v>116</v>
       </c>
       <c r="M12" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="G13">
-        <v>32263</v>
+        <v>21252</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
-      </c>
-      <c r="K13">
-        <v>12345</v>
-      </c>
-      <c r="L13">
-        <v>12345</v>
+        <v>123</v>
+      </c>
+      <c r="K13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L13" t="s">
+        <v>124</v>
       </c>
       <c r="M13" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="G14">
         <v>22163</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="L14" t="s">
+        <v>130</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="G15">
         <v>10163</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>12345</v>
+        <v>14</v>
+      </c>
+      <c r="K15" t="s">
+        <v>136</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="G16">
-        <v>33163</v>
+        <v>29901</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="I16" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16">
-        <v>12345</v>
-      </c>
-      <c r="L16">
-        <v>12346</v>
+        <v>14</v>
+      </c>
+      <c r="K16" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" t="s">
+        <v>105</v>
       </c>
       <c r="M16" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.25">
